--- a/Team-Data/2014-15/2-24-2014-15.xlsx
+++ b/Team-Data/2014-15/2-24-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,10 +818,10 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -775,7 +842,7 @@
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -969,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -984,16 +1051,16 @@
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1163,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
@@ -1172,10 +1239,10 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1294,7 +1361,7 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>4</v>
@@ -1330,10 +1397,10 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
@@ -1533,7 +1600,7 @@
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1589,37 +1656,37 @@
         <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
         <v>0.458</v>
       </c>
       <c r="L7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="N7" t="n">
         <v>0.355</v>
       </c>
       <c r="O7" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P7" t="n">
         <v>24.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
         <v>21.9</v>
@@ -1637,7 +1704,7 @@
         <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA7" t="n">
         <v>20.9</v>
@@ -1646,13 +1713,13 @@
         <v>102.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1679,10 +1746,10 @@
         <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
@@ -1694,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1706,7 +1773,7 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>25</v>
@@ -1715,10 +1782,10 @@
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.672</v>
+        <v>0.655</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1795,19 +1862,19 @@
         <v>0.759</v>
       </c>
       <c r="R8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U8" t="n">
         <v>22.9</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
@@ -1816,10 +1883,10 @@
         <v>4.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA8" t="n">
         <v>21.8</v>
@@ -1828,7 +1895,7 @@
         <v>105.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1861,7 +1928,7 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1876,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1894,10 +1961,10 @@
         <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,7 +2092,7 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2049,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
@@ -2061,7 +2128,7 @@
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>17</v>
@@ -2076,7 +2143,7 @@
         <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.404</v>
+        <v>0.411</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,10 +2202,10 @@
         <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L10" t="n">
         <v>8.699999999999999</v>
@@ -2147,34 +2214,34 @@
         <v>25.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O10" t="n">
         <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.706</v>
+        <v>0.709</v>
       </c>
       <c r="R10" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T10" t="n">
         <v>45.3</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V10" t="n">
         <v>13.6</v>
       </c>
       <c r="W10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
         <v>4.4</v>
@@ -2186,25 +2253,25 @@
         <v>18.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>18</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
@@ -2213,7 +2280,7 @@
         <v>22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2258,13 +2325,13 @@
         <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="J11" t="n">
         <v>87</v>
@@ -2326,61 +2393,61 @@
         <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="O11" t="n">
         <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="U11" t="n">
         <v>27.1</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
         <v>9.4</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
         <v>3.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
         <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="AC11" t="n">
         <v>10.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2425,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2437,13 +2504,13 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,19 +2575,19 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.717</v>
+        <v>0.715</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.1</v>
+        <v>103.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2574,10 +2641,10 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>13</v>
@@ -2622,19 +2689,19 @@
         <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.404</v>
+        <v>0.411</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,13 +2748,13 @@
         <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K13" t="n">
         <v>0.437</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
         <v>20.8</v>
@@ -2696,25 +2763,25 @@
         <v>0.335</v>
       </c>
       <c r="O13" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R13" t="n">
         <v>10.5</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
         <v>44.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
@@ -2723,43 +2790,43 @@
         <v>6.1</v>
       </c>
       <c r="X13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y13" t="n">
         <v>4.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>18</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2777,43 +2844,43 @@
         <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -2926,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.259</v>
+        <v>0.255</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
         <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y15" t="n">
         <v>4.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>24</v>
@@ -3135,16 +3202,16 @@
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
@@ -3153,13 +3220,13 @@
         <v>17</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
         <v>19</v>
@@ -3168,16 +3235,16 @@
         <v>19</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3329,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>12</v>
@@ -3350,7 +3417,7 @@
         <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3508,7 +3575,7 @@
         <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3538,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
         <v>10</v>
@@ -3690,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
         <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.509</v>
+        <v>0.518</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,70 +4022,70 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
         <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
         <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W20" t="n">
         <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
@@ -4027,16 +4094,16 @@
         <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
@@ -4045,25 +4112,25 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
@@ -4072,10 +4139,10 @@
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>27</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>18</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4251,10 +4318,10 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J22" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K22" t="n">
         <v>0.445</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
         <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O22" t="n">
         <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R22" t="n">
         <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="T22" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V22" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4367,19 +4434,19 @@
         <v>4.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
         <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.3</v>
+        <v>101.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,13 +4458,13 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4412,7 +4479,7 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
@@ -4421,10 +4488,10 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -4433,25 +4500,25 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
@@ -4522,31 +4589,31 @@
         <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
@@ -4555,13 +4622,13 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -4576,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,13 +4691,13 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>23</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>20</v>
-      </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>9</v>
@@ -4800,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4809,10 +4876,10 @@
         <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4961,25 +5028,25 @@
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR25" t="n">
         <v>15</v>
       </c>
       <c r="AS25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT25" t="n">
         <v>19</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5116,7 +5183,7 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5152,7 +5219,7 @@
         <v>16</v>
       </c>
       <c r="AS26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT26" t="n">
         <v>3</v>
@@ -5164,13 +5231,13 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5331,7 +5398,7 @@
         <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>5</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
         <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.607</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,43 +5478,43 @@
         <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O28" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
@@ -5459,7 +5526,7 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA28" t="n">
         <v>19.7</v>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5483,13 +5550,13 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
         <v>12</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>12</v>
@@ -5516,16 +5583,16 @@
         <v>24</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5546,7 +5613,7 @@
         <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>0.649</v>
+        <v>0.661</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
@@ -5608,34 +5675,34 @@
         <v>0.348</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P29" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S29" t="n">
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U29" t="n">
         <v>20.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W29" t="n">
         <v>7.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
         <v>5.2</v>
@@ -5644,37 +5711,37 @@
         <v>21.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.7</v>
+        <v>104.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF29" t="n">
         <v>5</v>
       </c>
-      <c r="AF29" t="n">
-        <v>7</v>
-      </c>
       <c r="AG29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>8</v>
       </c>
       <c r="AJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK29" t="n">
         <v>13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5692,10 +5759,10 @@
         <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
@@ -5707,16 +5774,16 @@
         <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX29" t="n">
         <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
         <v>23</v>
@@ -5889,16 +5956,16 @@
         <v>29</v>
       </c>
       <c r="AV30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
         <v>22</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
         <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>0.579</v>
+        <v>0.589</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
@@ -5960,16 +6027,16 @@
         <v>82.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>16.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O31" t="n">
         <v>16</v>
@@ -5978,7 +6045,7 @@
         <v>21.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R31" t="n">
         <v>10.5</v>
@@ -5993,34 +6060,34 @@
         <v>24.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W31" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6053,13 +6120,13 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6071,22 +6138,22 @@
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-24-2014-15</t>
+          <t>2015-02-24</t>
         </is>
       </c>
     </row>
